--- a/docs/case_files/CASE_BTW.xlsx
+++ b/docs/case_files/CASE_BTW.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -784,6 +784,92 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>BscScan top holders | contract verify L-28 | Nansen (LOCKED) | depth snap #2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE (R7 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>first_nn LSR (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>first_nn OI (fapi 30d)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N/A-GAP dates (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-24, 2026-07-25, 2026-07-26, 2026-08-08, 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>N/A-RETENTION rule</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Trước first_nn = N/A-RETENTION (store không cover, không collect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CORRECTIONS (R8 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gap 24-26/07 nguồn store</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3 ngày freshwatch drop toàn universe — không sửa lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schema v2.1 append cols 51-52</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd + spot_ext_venue = CHƯA-TRA · chờ nhịp 2 R5</t>
         </is>
       </c>
     </row>
@@ -798,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX68"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -904,6 +990,11 @@
           <t>B-2 DIAGNOSTIC FLAGS (dump analysis)</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SPOT-EXT (v2.1 R4 21/08)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1156,6 +1247,16 @@
           <t>flag_knife_crowd (gLSR↑&amp;ret&lt;-3%)</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>spot_ext_venue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -1179,10 +1280,10 @@
         <v>0.054378</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>356780500.22918</v>
+        <v>356780500.23</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>51.2671</v>
+        <v>51.3496</v>
       </c>
       <c r="I3" s="14" t="n">
         <v>-4.151e-05</v>
@@ -1290,6 +1391,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -1313,10 +1424,10 @@
         <v>0.054026</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>158319170.009083</v>
+        <v>158319170.01</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>50.0857</v>
+        <v>50.1312</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>0.00028537</v>
@@ -1440,6 +1551,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1463,10 +1584,10 @@
         <v>0.06390899999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>213229721.268252</v>
+        <v>213229721.27</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>50.2359</v>
+        <v>50.316</v>
       </c>
       <c r="I5" s="14" t="n">
         <v>0.00047846</v>
@@ -1586,6 +1707,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -1609,10 +1740,10 @@
         <v>0.060557</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>134308360.039584</v>
+        <v>134308360.04</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>49.2067</v>
+        <v>49.302</v>
       </c>
       <c r="I6" s="14" t="n">
         <v>0.0007471999999999999</v>
@@ -1734,6 +1865,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -1757,10 +1898,10 @@
         <v>0.094986</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>121388748.523974</v>
+        <v>121388748.52</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>51.7875</v>
+        <v>51.9679</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>0.0003528</v>
@@ -1886,6 +2027,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -1909,10 +2060,10 @@
         <v>0.08419</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>392268324.44301</v>
+        <v>392268324.44</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>49.7463</v>
+        <v>49.891</v>
       </c>
       <c r="I8" s="14" t="n">
         <v>0.00029521</v>
@@ -2038,6 +2189,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -2061,10 +2222,10 @@
         <v>0.08239</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>101518817.362523</v>
+        <v>101518817.36</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>49.1602</v>
+        <v>49.2032</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>0.00038684</v>
@@ -2192,6 +2353,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -2215,10 +2386,10 @@
         <v>0.07012</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>34770690.298599</v>
+        <v>34770690.3</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>48.2474</v>
+        <v>48.3335</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>0.00031987</v>
@@ -2346,6 +2517,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -2369,10 +2550,10 @@
         <v>0.0864</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>36210741.285133</v>
+        <v>36210741.29</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>51.4906</v>
+        <v>51.5407</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>0.00015952</v>
@@ -2500,6 +2681,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -2523,10 +2714,10 @@
         <v>0.09517</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>54858828.524474</v>
+        <v>54858828.52</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>48.963</v>
+        <v>49.0504</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>0.0002086</v>
@@ -2654,6 +2845,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2677,10 +2878,10 @@
         <v>0.09072</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>13530994.715772</v>
+        <v>13530994.72</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>49.3703</v>
+        <v>49.4296</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>0.00018857</v>
@@ -2808,6 +3009,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2831,10 +3042,10 @@
         <v>0.05907</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>45794630.117451</v>
+        <v>45794630.12</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>48.0841</v>
+        <v>48.2104</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>1.233e-05</v>
@@ -2962,6 +3173,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2985,10 +3206,10 @@
         <v>0.04814</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>55878871.570656</v>
+        <v>55878871.57</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>47.5129</v>
+        <v>47.6499</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>5e-05</v>
@@ -3116,6 +3337,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3139,10 +3370,10 @@
         <v>0.05151</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>63245888.075271</v>
+        <v>63245888.08</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>46.9912</v>
+        <v>47.0167</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>0.0012018</v>
@@ -3270,6 +3501,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -3293,10 +3534,10 @@
         <v>0.09802</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>146328839.438272</v>
+        <v>146328839.44</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>50.5478</v>
+        <v>50.7929</v>
       </c>
       <c r="I17" s="14" t="n">
         <v>0.00175537</v>
@@ -3430,6 +3671,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -3453,10 +3704,10 @@
         <v>0.13325</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>756450727.985195</v>
+        <v>756450727.99</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>51.2708</v>
+        <v>51.3138</v>
       </c>
       <c r="I18" s="14" t="n">
         <v>0.00264236</v>
@@ -3590,6 +3841,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -3613,10 +3874,10 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>481917988.844401</v>
+        <v>481917988.84</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>49.1232</v>
+        <v>49.2273</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>0.00117739</v>
@@ -3750,6 +4011,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -3773,10 +4044,10 @@
         <v>0.09419</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>246405793.03859</v>
+        <v>246405793.04</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>49.7899</v>
+        <v>49.8388</v>
       </c>
       <c r="I20" s="14" t="n">
         <v>0.00072344</v>
@@ -3906,6 +4177,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -3929,10 +4210,10 @@
         <v>0.09999</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104030549.411766</v>
+        <v>104030549.41</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>49.7732</v>
+        <v>49.8905</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>0.00047623</v>
@@ -4062,6 +4343,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -4085,10 +4376,10 @@
         <v>0.10126</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>128266534.679026</v>
+        <v>128266534.68</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>49.136</v>
+        <v>49.2557</v>
       </c>
       <c r="I22" s="14" t="n">
         <v>0.0002306</v>
@@ -4218,6 +4509,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -4241,10 +4542,10 @@
         <v>0.0968</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>75116275.602305</v>
+        <v>75116275.59999999</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>49.1709</v>
+        <v>49.2263</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>0.00012818</v>
@@ -4374,6 +4675,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4397,10 +4708,10 @@
         <v>0.09632</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>48048621.400001</v>
+        <v>48048621.4</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>48.0481</v>
+        <v>48.031</v>
       </c>
       <c r="I24" s="14" t="n">
         <v>-0.00097605</v>
@@ -4530,6 +4841,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4553,10 +4874,10 @@
         <v>0.06448</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>37305249.563888</v>
+        <v>37305249.56</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>47.3704</v>
+        <v>47.5459</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>-0.00013261</v>
@@ -4686,6 +5007,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -4709,10 +5040,10 @@
         <v>0.05709</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>38927654.761813</v>
+        <v>38927654.76</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>48.0233</v>
+        <v>48.1085</v>
       </c>
       <c r="I26" s="14" t="n">
         <v>5e-05</v>
@@ -4842,6 +5173,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -4865,10 +5206,10 @@
         <v>0.05024</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>25381466.58333</v>
+        <v>25381466.58</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>47.8372</v>
+        <v>47.8853</v>
       </c>
       <c r="I27" s="14" t="n">
         <v>5e-05</v>
@@ -4998,6 +5339,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -5021,10 +5372,10 @@
         <v>0.05268</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>91305567.988786</v>
+        <v>91305567.98999999</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>47.2674</v>
+        <v>47.3619</v>
       </c>
       <c r="I28" s="14" t="n">
         <v>8.067999999999999e-05</v>
@@ -5154,6 +5505,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -5177,10 +5538,10 @@
         <v>0.06716999999999999</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>60521040.387357</v>
+        <v>60521040.39</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>48.7223</v>
+        <v>48.7785</v>
       </c>
       <c r="I29" s="14" t="n">
         <v>0.00014586</v>
@@ -5310,6 +5671,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -5333,10 +5704,10 @@
         <v>0.06236</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>21609429.538806</v>
+        <v>21609429.54</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>46.3988</v>
+        <v>46.453</v>
       </c>
       <c r="I30" s="14" t="n">
         <v>0.00020076</v>
@@ -5466,6 +5837,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -5489,10 +5870,10 @@
         <v>0.06222</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>15990403.108902</v>
+        <v>15990403.11</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>47.8989</v>
+        <v>47.9984</v>
       </c>
       <c r="I31" s="14" t="n">
         <v>0.00016102</v>
@@ -5626,6 +6007,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -5649,10 +6040,10 @@
         <v>0.06458999999999999</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>14128167.126436</v>
+        <v>14128167.13</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>49.112</v>
+        <v>49.1379</v>
       </c>
       <c r="I32" s="14" t="n">
         <v>0.00014775</v>
@@ -5782,6 +6173,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -5805,10 +6206,10 @@
         <v>0.07584</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>89783749.840918</v>
+        <v>89783749.84</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>48.5244</v>
+        <v>48.5344</v>
       </c>
       <c r="I33" s="14" t="n">
         <v>0.00030654</v>
@@ -5938,6 +6339,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -5961,10 +6372,10 @@
         <v>0.06034</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>30394597.668636</v>
+        <v>30394597.67</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>45.7404</v>
+        <v>45.7997</v>
       </c>
       <c r="I34" s="14" t="n">
         <v>0.00022392</v>
@@ -6094,6 +6505,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -6117,10 +6538,10 @@
         <v>0.06217</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>12367091.157708</v>
+        <v>12367091.16</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>46.8382</v>
+        <v>46.8618</v>
       </c>
       <c r="I35" s="14" t="n">
         <v>0.00012189</v>
@@ -6250,6 +6671,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -6273,10 +6704,10 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14515992.354175</v>
+        <v>14515992.35</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>46.9383</v>
+        <v>46.9864</v>
       </c>
       <c r="I36" s="14" t="n">
         <v>0.00017484</v>
@@ -6406,6 +6837,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -6429,10 +6870,10 @@
         <v>0.06494</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7073200.16733</v>
+        <v>7073200.17</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>47.4921</v>
+        <v>47.518</v>
       </c>
       <c r="I37" s="14" t="n">
         <v>0.00025709</v>
@@ -6562,6 +7003,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -6585,10 +7036,10 @@
         <v>0.06426999999999999</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5574091.96751</v>
+        <v>5574091.97</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>47.9083</v>
+        <v>47.9379</v>
       </c>
       <c r="I38" s="14" t="n">
         <v>0.0001595</v>
@@ -6718,6 +7169,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -6741,10 +7202,10 @@
         <v>0.05932</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>5657344.12225</v>
+        <v>5657344.12</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>47.0392</v>
+        <v>47.1408</v>
       </c>
       <c r="I39" s="14" t="n">
         <v>0.00033553</v>
@@ -6874,6 +7335,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -6897,10 +7368,10 @@
         <v>0.06013</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>4849031.896912</v>
+        <v>4849031.9</v>
       </c>
       <c r="H40" s="14" t="n">
-        <v>46.6316</v>
+        <v>46.7005</v>
       </c>
       <c r="I40" s="14" t="n">
         <v>0.00027555</v>
@@ -7034,6 +7505,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -7057,10 +7538,10 @@
         <v>0.06073</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4663971.157313</v>
+        <v>4663971.16</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>49.5204</v>
+        <v>49.5264</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>0.00017765</v>
@@ -7198,6 +7679,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -7221,10 +7712,10 @@
         <v>0.0584</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3746951.805176</v>
+        <v>3746951.81</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>45.0823</v>
+        <v>45.08</v>
       </c>
       <c r="I42" s="14" t="n">
         <v>0.00022492</v>
@@ -7358,6 +7849,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -7381,10 +7882,10 @@
         <v>0.06021</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>7966832.213818</v>
+        <v>7966832.21</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>47.2938</v>
+        <v>47.3762</v>
       </c>
       <c r="I43" s="14" t="n">
         <v>0.00033477</v>
@@ -7518,6 +8019,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -7541,10 +8052,10 @@
         <v>0.05996</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>3776191.73874</v>
+        <v>3776191.74</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>47.8292</v>
+        <v>47.8475</v>
       </c>
       <c r="I44" s="14" t="n">
         <v>0.00025756</v>
@@ -7678,6 +8189,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -7701,10 +8222,10 @@
         <v>0.0602</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>3859729.785063</v>
+        <v>3859729.79</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>47.2233</v>
+        <v>47.2737</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>0.00025285</v>
@@ -7838,6 +8359,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -7861,10 +8392,10 @@
         <v>0.06325</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>14213403.879562</v>
+        <v>14213403.88</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>46.7356</v>
+        <v>46.7352</v>
       </c>
       <c r="I46" s="14" t="n">
         <v>0.00034718</v>
@@ -7998,6 +8529,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -8021,10 +8562,10 @@
         <v>0.06869</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>8717291.461112</v>
+        <v>8717291.460000001</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>48.5523</v>
+        <v>48.5904</v>
       </c>
       <c r="I47" s="14" t="n">
         <v>0.0002945</v>
@@ -8160,6 +8701,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -8183,10 +8734,10 @@
         <v>0.06778000000000001</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>8094839.548676</v>
+        <v>8094839.55</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>47.8568</v>
+        <v>47.8741</v>
       </c>
       <c r="I48" s="14" t="n">
         <v>0.00033291</v>
@@ -8322,6 +8873,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -8345,10 +8906,10 @@
         <v>0.07102</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>11774434.338918</v>
+        <v>11774434.34</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>48.6643</v>
+        <v>48.6742</v>
       </c>
       <c r="I49" s="14" t="n">
         <v>0.00031998</v>
@@ -8486,6 +9047,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -8509,10 +9080,10 @@
         <v>0.06671000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>8994590.911320001</v>
+        <v>8994590.91</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>47.0583</v>
+        <v>47.0909</v>
       </c>
       <c r="I50" s="14" t="n">
         <v>0.00026002</v>
@@ -8650,6 +9221,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -8673,10 +9254,10 @@
         <v>0.06637</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>3179663.438148</v>
+        <v>3179663.44</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>48.8483</v>
+        <v>48.8607</v>
       </c>
       <c r="I51" s="14" t="n">
         <v>0.00017021</v>
@@ -8814,6 +9395,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -8837,10 +9428,10 @@
         <v>0.06705</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>7214690.873406</v>
+        <v>7214690.87</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>48.9001</v>
+        <v>48.8564</v>
       </c>
       <c r="I52" s="14" t="n">
         <v>0.00013698</v>
@@ -8886,9 +9477,15 @@
       <c r="X52" s="14" t="inlineStr"/>
       <c r="Y52" s="14" t="inlineStr"/>
       <c r="Z52" s="14" t="inlineStr"/>
-      <c r="AA52" s="14" t="inlineStr"/>
-      <c r="AB52" s="14" t="inlineStr"/>
-      <c r="AC52" s="14" t="inlineStr"/>
+      <c r="AA52" s="14" t="n">
+        <v>1.8908</v>
+      </c>
+      <c r="AB52" s="14" t="n">
+        <v>1.9638</v>
+      </c>
+      <c r="AC52" s="14" t="n">
+        <v>1.9958</v>
+      </c>
       <c r="AD52" s="14" t="inlineStr"/>
       <c r="AE52" s="14" t="inlineStr"/>
       <c r="AF52" s="14" t="inlineStr"/>
@@ -8927,7 +9524,7 @@
       </c>
       <c r="AP52" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ52" s="14" t="n">
@@ -8960,6 +9557,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -8983,10 +9590,10 @@
         <v>0.07768</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>5845516.500867</v>
+        <v>5845516.5</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>49.936</v>
+        <v>49.9927</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>0.00010318</v>
@@ -9032,9 +9639,15 @@
       <c r="X53" s="14" t="inlineStr"/>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="inlineStr"/>
-      <c r="AA53" s="14" t="inlineStr"/>
-      <c r="AB53" s="14" t="inlineStr"/>
-      <c r="AC53" s="14" t="inlineStr"/>
+      <c r="AA53" s="14" t="n">
+        <v>1.8629</v>
+      </c>
+      <c r="AB53" s="14" t="n">
+        <v>1.9647</v>
+      </c>
+      <c r="AC53" s="14" t="n">
+        <v>2.0998</v>
+      </c>
       <c r="AD53" s="14" t="inlineStr"/>
       <c r="AE53" s="14" t="inlineStr"/>
       <c r="AF53" s="14" t="inlineStr"/>
@@ -9073,7 +9686,7 @@
       </c>
       <c r="AP53" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ53" s="14" t="n">
@@ -9106,6 +9719,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -9129,10 +9752,10 @@
         <v>0.07163</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>12049632.515185</v>
+        <v>12049632.52</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>46.79</v>
+        <v>46.8252</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.00019788</v>
@@ -9178,9 +9801,15 @@
       <c r="X54" s="14" t="inlineStr"/>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="inlineStr"/>
-      <c r="AA54" s="14" t="inlineStr"/>
-      <c r="AB54" s="14" t="inlineStr"/>
-      <c r="AC54" s="14" t="inlineStr"/>
+      <c r="AA54" s="14" t="n">
+        <v>1.7714</v>
+      </c>
+      <c r="AB54" s="14" t="n">
+        <v>1.7801</v>
+      </c>
+      <c r="AC54" s="14" t="n">
+        <v>1.8794</v>
+      </c>
       <c r="AD54" s="14" t="inlineStr"/>
       <c r="AE54" s="14" t="inlineStr"/>
       <c r="AF54" s="14" t="inlineStr"/>
@@ -9219,7 +9848,7 @@
       </c>
       <c r="AP54" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ54" s="14" t="n">
@@ -9252,6 +9881,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -9275,10 +9914,10 @@
         <v>0.07423</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>169458262.188905</v>
+        <v>169458262.19</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>49.757</v>
+        <v>49.8964</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.0004205</v>
@@ -9410,6 +10049,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -9433,10 +10082,10 @@
         <v>0.09014999999999999</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>55828590.773377</v>
+        <v>55828590.77</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>48.0243</v>
+        <v>48.1028</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.00017213</v>
@@ -9568,6 +10217,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -9591,10 +10250,10 @@
         <v>0.08298999999999999</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>91871488.22597601</v>
+        <v>91871488.23</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>48.6491</v>
+        <v>48.6815</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0.00024563</v>
@@ -9726,6 +10385,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -9749,10 +10418,10 @@
         <v>0.08484999999999999</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>24122011.31322</v>
+        <v>24122011.31</v>
       </c>
       <c r="H58" s="14" t="n">
-        <v>47.388</v>
+        <v>47.4666</v>
       </c>
       <c r="I58" s="14" t="n">
         <v>0.00020471</v>
@@ -9888,6 +10557,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -9911,10 +10590,10 @@
         <v>0.10171</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>15347354.407173</v>
+        <v>15347354.41</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>49.2461</v>
+        <v>49.4499</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>0.00021222</v>
@@ -10050,6 +10729,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -10073,10 +10762,10 @@
         <v>0.09113</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>129045425.840596</v>
+        <v>129045425.84</v>
       </c>
       <c r="H60" s="14" t="n">
-        <v>49.395</v>
+        <v>49.433</v>
       </c>
       <c r="I60" s="14" t="n">
         <v>0.00047628</v>
@@ -10214,6 +10903,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -10237,10 +10936,10 @@
         <v>0.08044</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>49484316.643368</v>
+        <v>49484316.64</v>
       </c>
       <c r="H61" s="14" t="n">
-        <v>48.8425</v>
+        <v>48.9063</v>
       </c>
       <c r="I61" s="14" t="n">
         <v>0.00041937</v>
@@ -10378,6 +11077,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -10401,10 +11110,10 @@
         <v>0.10626</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>60641891.204407</v>
+        <v>60641891.2</v>
       </c>
       <c r="H62" s="14" t="n">
-        <v>50.3879</v>
+        <v>50.4617</v>
       </c>
       <c r="I62" s="14" t="n">
         <v>0.00037487</v>
@@ -10542,6 +11251,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -10565,10 +11284,10 @@
         <v>0.13495</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>95968473.433924</v>
+        <v>95968473.43000001</v>
       </c>
       <c r="H63" s="14" t="n">
-        <v>51.6804</v>
+        <v>51.7496</v>
       </c>
       <c r="I63" s="14" t="n">
         <v>0.00048782</v>
@@ -10706,6 +11425,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -10729,10 +11458,10 @@
         <v>0.16263</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>84641552.118626</v>
+        <v>84641552.12</v>
       </c>
       <c r="H64" s="14" t="n">
-        <v>51.7145</v>
+        <v>51.8765</v>
       </c>
       <c r="I64" s="14" t="n">
         <v>0.00062331</v>
@@ -10870,6 +11599,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -10893,10 +11632,10 @@
         <v>0.19359</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>82545927.8196</v>
+        <v>82545927.81999999</v>
       </c>
       <c r="H65" s="14" t="n">
-        <v>50.8374</v>
+        <v>50.9421</v>
       </c>
       <c r="I65" s="14" t="n">
         <v>0.00074755</v>
@@ -11034,6 +11773,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -11057,10 +11806,10 @@
         <v>0.224</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>72749696.41481601</v>
+        <v>72749696.41</v>
       </c>
       <c r="H66" s="14" t="n">
-        <v>52.1403</v>
+        <v>52.2624</v>
       </c>
       <c r="I66" s="14" t="n">
         <v>0.00060321</v>
@@ -11198,6 +11947,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
@@ -11221,10 +11980,10 @@
         <v>0.20437</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>198297570.752068</v>
+        <v>198297570.75</v>
       </c>
       <c r="H67" s="14" t="n">
-        <v>49.6982</v>
+        <v>49.813</v>
       </c>
       <c r="I67" s="14" t="n">
         <v>0.00080299</v>
@@ -11270,10 +12029,18 @@
       <c r="X67" s="14" t="inlineStr"/>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="inlineStr"/>
-      <c r="AA67" s="14" t="inlineStr"/>
-      <c r="AB67" s="14" t="inlineStr"/>
-      <c r="AC67" s="14" t="inlineStr"/>
-      <c r="AD67" s="14" t="inlineStr"/>
+      <c r="AA67" s="14" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="AB67" s="14" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="AC67" s="14" t="n">
+        <v>0.6595</v>
+      </c>
+      <c r="AD67" s="14" t="n">
+        <v>0.988</v>
+      </c>
       <c r="AE67" s="14" t="inlineStr"/>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -11311,7 +12078,7 @@
       </c>
       <c r="AP67" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ67" s="14" t="n">
@@ -11344,6 +12111,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -11367,10 +12144,10 @@
         <v>0.21484</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>101352521.18075</v>
+        <v>101352521.18</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>50.8102</v>
+        <v>50.9542</v>
       </c>
       <c r="I68" s="14" t="n">
         <v>0.00109098</v>
@@ -11416,10 +12193,18 @@
       <c r="X68" s="14" t="inlineStr"/>
       <c r="Y68" s="14" t="inlineStr"/>
       <c r="Z68" s="14" t="inlineStr"/>
-      <c r="AA68" s="14" t="inlineStr"/>
-      <c r="AB68" s="14" t="inlineStr"/>
-      <c r="AC68" s="14" t="inlineStr"/>
-      <c r="AD68" s="14" t="inlineStr"/>
+      <c r="AA68" s="14" t="n">
+        <v>1.7388</v>
+      </c>
+      <c r="AB68" s="14" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="AC68" s="14" t="n">
+        <v>0.7966</v>
+      </c>
+      <c r="AD68" s="14" t="n">
+        <v>1.0329</v>
+      </c>
       <c r="AE68" s="14" t="inlineStr"/>
       <c r="AF68" s="14" t="inlineStr"/>
       <c r="AG68" s="14" t="inlineStr"/>
@@ -11457,7 +12242,7 @@
       </c>
       <c r="AP68" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ68" s="14" t="n">
@@ -11488,6 +12273,860 @@
       <c r="AX68" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.03092667</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.01965</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.016559</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.036721</v>
+      </c>
+      <c r="G69" t="n">
+        <v>79015506.34999999</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50.2815</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.0006711</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.00051203</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.00083018</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.19449667</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.19679</v>
+      </c>
+      <c r="G70" t="n">
+        <v>62297647.48</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50.1204</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.00089913</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.00062363</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.00119274</v>
+      </c>
+      <c r="L70" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" t="n">
+        <v>46863970.8636</v>
+      </c>
+      <c r="N70" t="n">
+        <v>218134290</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.8029</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.7449</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.0008</v>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.19454667</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.19679</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.20564</v>
+      </c>
+      <c r="G71" t="n">
+        <v>39453836.31</v>
+      </c>
+      <c r="H71" t="n">
+        <v>49.5572</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.00054789</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.00043748</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.0007092999999999999</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>42938504.51055</v>
+      </c>
+      <c r="N71" t="n">
+        <v>218194545</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.8126</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.8188</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.23788333</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.20565</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="G72" t="n">
+        <v>136044313.16</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50.4231</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.00081455</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.00050029</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.0013696</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" t="n">
+        <v>46832901.00313</v>
+      </c>
+      <c r="N72" t="n">
+        <v>227753251</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.8064</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.25686</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.19782</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="G73" t="n">
+        <v>116771420.39</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50.2178</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.00079809</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.00055301</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.00100874</v>
+      </c>
+      <c r="L73" t="n">
+        <v>6</v>
+      </c>
+      <c r="M73" t="n">
+        <v>61654255.61127</v>
+      </c>
+      <c r="N73" t="n">
+        <v>236576707</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.5707</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.6493</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.27411</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="G74" t="n">
+        <v>104456135.51</v>
+      </c>
+      <c r="H74" t="n">
+        <v>51.2903</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.00076185</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.00010509</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.00109806</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6</v>
+      </c>
+      <c r="M74" t="n">
+        <v>68697523.65124001</v>
+      </c>
+      <c r="N74" t="n">
+        <v>250519742</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1.6541</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.0533</v>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="G75" t="n">
+        <v>71981993.08</v>
+      </c>
+      <c r="H75" t="n">
+        <v>49.4155</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.00090814</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.0006671099999999999</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.00120997</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>76485235.87998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>245949051</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.6607</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5853</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.36672667</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="G76" t="n">
+        <v>142240783.43</v>
+      </c>
+      <c r="H76" t="n">
+        <v>51.1085</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.00103947</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.00077269</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.00166829</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6</v>
+      </c>
+      <c r="M76" t="n">
+        <v>78775040.92639156</v>
+      </c>
+      <c r="N76" t="n">
+        <v>259466738</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.5601</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.0407</v>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.37212333</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="G77" t="n">
+        <v>214136953.18</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50.8898</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.0008535</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.00030426</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.00171533</v>
+      </c>
+      <c r="L77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>112496458.24404</v>
+      </c>
+      <c r="N77" t="n">
+        <v>281776521</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>1.4937</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.0326</v>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.40382333</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="G78" t="n">
+        <v>94130267.33</v>
+      </c>
+      <c r="H78" t="n">
+        <v>51.9821</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.00036484</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.00021912</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.00067982</v>
+      </c>
+      <c r="L78" t="n">
+        <v>6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>93178538.7722826</v>
+      </c>
+      <c r="N78" t="n">
+        <v>260124020</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1.6779</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.5349</v>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.49381333</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.77888</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1326836395.48</v>
+      </c>
+      <c r="H79" t="n">
+        <v>51.3032</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.00078791</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.00051687</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.00141401</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6</v>
+      </c>
+      <c r="M79" t="n">
+        <v>113524912.19094</v>
+      </c>
+      <c r="N79" t="n">
+        <v>261994674</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1.5284</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.46335</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="G80" t="n">
+        <v>396080028.1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50.8464</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.00035845</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.00027365</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.00049219</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>83906113.75956</v>
+      </c>
+      <c r="N80" t="n">
+        <v>215442186</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1.6735</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_BTW.xlsx
+++ b/docs/case_files/CASE_BTW.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -870,6 +870,80 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>vol_spot_ext_usd + spot_ext_venue = CHƯA-TRA · chờ nhịp 2 R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>META (V5 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>v2+ext-20260821 (v2 cols 1-50 + R4 append cols 51-52 CHƯA-TRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>consumer_rule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Consumer đọc theo HEADER row 2 field names (không hardcode col index). Cols 42+ append-only per L-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE UPDATE (V4 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>lsr_null_dates (2)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-04, 2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OI first_nn (real)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OI last_nn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
